--- a/test_Data/userData.xlsx
+++ b/test_Data/userData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AU-Demo-project\Playwright_POC\test_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA205DB-BE4E-4C81-81AD-E22080773EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68768016-7136-428F-A406-23219FFD5687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E278AF0B-43C1-40CB-A458-58E602D7B0C7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
   <si>
     <t>Email</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>Test@123</t>
+  </si>
+  <si>
+    <t>maniteja1327@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -417,7 +420,7 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" customWidth="1"/>
+    <col min="1" max="1" width="38.1796875" customWidth="1"/>
     <col min="2" max="2" width="25.6328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -439,7 +442,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -455,7 +458,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
@@ -480,6 +483,8 @@
     <hyperlink ref="B4" r:id="rId6" xr:uid="{6FB58A39-FDFF-4630-B782-885DDE973385}"/>
     <hyperlink ref="B5" r:id="rId7" xr:uid="{5A220AB9-602A-4B9D-BA4F-B9012AA7BFAD}"/>
     <hyperlink ref="B6" r:id="rId8" xr:uid="{05B8D2A0-D532-4FB9-BEE0-82A28ACE03C9}"/>
+    <hyperlink ref="A3" r:id="rId9" xr:uid="{6773F78F-2C50-4A42-99E5-810E46F68174}"/>
+    <hyperlink ref="A5" r:id="rId10" xr:uid="{A6FE49CC-6D23-471E-A7A0-003F37DE77AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
